--- a/output_5a.xlsx
+++ b/output_5a.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>354202.9</v>
+        <v>354296.6</v>
       </c>
     </row>
     <row r="4">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21270</v>
+        <v>21180</v>
       </c>
     </row>
     <row r="8">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>510072.9</v>
+        <v>510076.6</v>
       </c>
     </row>
     <row r="9">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14.18</v>
+        <v>14.12</v>
       </c>
     </row>
   </sheetData>
@@ -597,10 +597,10 @@
         <v>30000</v>
       </c>
       <c r="D2" t="n">
-        <v>41191</v>
+        <v>41182</v>
       </c>
       <c r="E2" t="n">
-        <v>71191</v>
+        <v>71182</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -620,10 +620,10 @@
         <v>17500</v>
       </c>
       <c r="D3" t="n">
-        <v>21109.9</v>
+        <v>21107.8</v>
       </c>
       <c r="E3" t="n">
-        <v>38609.9</v>
+        <v>38607.8</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -689,10 +689,10 @@
         <v>10000</v>
       </c>
       <c r="D6" t="n">
-        <v>69440</v>
+        <v>69526.8</v>
       </c>
       <c r="E6" t="n">
-        <v>79440</v>
+        <v>79526.8</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -735,10 +735,10 @@
         <v>22500</v>
       </c>
       <c r="D8" t="n">
-        <v>137262</v>
+        <v>137280</v>
       </c>
       <c r="E8" t="n">
-        <v>159762</v>
+        <v>159780</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -758,10 +758,10 @@
         <v>132000</v>
       </c>
       <c r="D9" t="n">
-        <v>354202.9</v>
+        <v>354296.6</v>
       </c>
       <c r="E9" t="n">
-        <v>486202.9</v>
+        <v>486296.6</v>
       </c>
       <c r="F9" t="n">
         <v>600</v>
@@ -773,7 +773,7 @@
         <v>2000</v>
       </c>
       <c r="I9" t="n">
-        <v>21270</v>
+        <v>21180</v>
       </c>
     </row>
   </sheetData>
@@ -827,19 +827,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -847,19 +847,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -867,19 +867,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -887,19 +887,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -907,19 +907,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -927,19 +927,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -947,19 +947,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -970,16 +970,16 @@
         <v>300</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E9" t="n">
         <v>600</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -990,16 +990,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -1007,19 +1007,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="12">
@@ -1030,16 +1030,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -1050,16 +1050,16 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -1070,16 +1070,16 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -1090,16 +1090,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
@@ -1107,19 +1107,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="17">
@@ -1130,16 +1130,16 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1150,16 +1150,16 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="19">
@@ -1170,16 +1170,16 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="20">
@@ -1187,19 +1187,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="21">
@@ -1207,19 +1207,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="22">
@@ -1227,19 +1227,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="23">
@@ -1247,19 +1247,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="24">
@@ -1267,19 +1267,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="25">
@@ -1287,19 +1287,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="26">
@@ -1307,19 +1307,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="27">
@@ -1327,19 +1327,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="28">
@@ -1347,19 +1347,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="29">
@@ -1367,19 +1367,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="30">
@@ -1387,7 +1387,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1600</v>
+        <v>1616</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="G2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="H2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="I2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -1630,16 +1630,16 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="M2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="N2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="O2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -1648,13 +1648,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3652</v>
+        <v>3656</v>
       </c>
       <c r="S2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="T2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2000</v>
+        <v>2012</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1721,10 +1721,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="K3" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="Q3" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1754,10 +1754,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="V3" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5709</v>
+        <v>5712</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1912,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>19981.5</v>
+        <v>19992</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>19981.5</v>
+        <v>19971</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -2121,7 +2121,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2854.5</v>
+        <v>2856</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2854.5</v>
+        <v>2853</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -2224,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>951.5</v>
+        <v>952</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>951.5</v>
+        <v>951</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -2571,13 +2571,13 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="K2" t="n">
-        <v>7612</v>
+        <v>7608</v>
       </c>
       <c r="L2" t="n">
-        <v>11418</v>
+        <v>11412</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2589,13 +2589,13 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="Q2" t="n">
-        <v>7612</v>
+        <v>7608</v>
       </c>
       <c r="R2" t="n">
-        <v>11418</v>
+        <v>11412</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>3652</v>
+        <v>3656</v>
       </c>
       <c r="W2" t="n">
-        <v>7458</v>
+        <v>7460</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -2956,25 +2956,25 @@
         <v>3200</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3174,22 +3174,22 @@
         <v>398</v>
       </c>
       <c r="Q8" t="n">
-        <v>1181.5</v>
+        <v>1182</v>
       </c>
       <c r="R8" t="n">
-        <v>1000.5</v>
+        <v>1001</v>
       </c>
       <c r="S8" t="n">
-        <v>812.5</v>
+        <v>813</v>
       </c>
       <c r="T8" t="n">
-        <v>600.5</v>
+        <v>601</v>
       </c>
       <c r="U8" t="n">
-        <v>347.5</v>
+        <v>348</v>
       </c>
       <c r="V8" t="n">
-        <v>128.5</v>
+        <v>129</v>
       </c>
       <c r="W8" t="n">
         <v>884</v>

--- a/output_5a.xlsx
+++ b/output_5a.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>354202.9</v>
+        <v>354296.6</v>
       </c>
     </row>
     <row r="4">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21270</v>
+        <v>21180</v>
       </c>
     </row>
     <row r="8">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>510072.9</v>
+        <v>510076.6</v>
       </c>
     </row>
     <row r="9">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14.18</v>
+        <v>14.12</v>
       </c>
     </row>
   </sheetData>
@@ -597,10 +597,10 @@
         <v>30000</v>
       </c>
       <c r="D2" t="n">
-        <v>41191</v>
+        <v>41182</v>
       </c>
       <c r="E2" t="n">
-        <v>71191</v>
+        <v>71182</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -620,10 +620,10 @@
         <v>17500</v>
       </c>
       <c r="D3" t="n">
-        <v>21109.9</v>
+        <v>21107.8</v>
       </c>
       <c r="E3" t="n">
-        <v>38609.9</v>
+        <v>38607.8</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -689,10 +689,10 @@
         <v>10000</v>
       </c>
       <c r="D6" t="n">
-        <v>69440</v>
+        <v>69526.8</v>
       </c>
       <c r="E6" t="n">
-        <v>79440</v>
+        <v>79526.8</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -735,10 +735,10 @@
         <v>22500</v>
       </c>
       <c r="D8" t="n">
-        <v>137262</v>
+        <v>137280</v>
       </c>
       <c r="E8" t="n">
-        <v>159762</v>
+        <v>159780</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -758,10 +758,10 @@
         <v>132000</v>
       </c>
       <c r="D9" t="n">
-        <v>354202.9</v>
+        <v>354296.6</v>
       </c>
       <c r="E9" t="n">
-        <v>486202.9</v>
+        <v>486296.6</v>
       </c>
       <c r="F9" t="n">
         <v>600</v>
@@ -773,7 +773,7 @@
         <v>2000</v>
       </c>
       <c r="I9" t="n">
-        <v>21270</v>
+        <v>21180</v>
       </c>
     </row>
   </sheetData>
@@ -827,19 +827,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -847,19 +847,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -867,19 +867,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -887,19 +887,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -907,19 +907,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -927,19 +927,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -947,19 +947,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -970,16 +970,16 @@
         <v>300</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E9" t="n">
         <v>600</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -990,16 +990,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -1007,19 +1007,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="12">
@@ -1030,16 +1030,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -1050,16 +1050,16 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -1067,19 +1067,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -1087,19 +1087,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
@@ -1107,19 +1107,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="17">
@@ -1150,16 +1150,16 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="19">
@@ -1170,16 +1170,16 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="20">
@@ -1187,19 +1187,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="21">
@@ -1207,19 +1207,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="22">
@@ -1227,19 +1227,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="23">
@@ -1247,19 +1247,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="24">
@@ -1267,19 +1267,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="25">
@@ -1287,19 +1287,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="26">
@@ -1307,19 +1307,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="27">
@@ -1327,19 +1327,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="28">
@@ -1347,19 +1347,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="29">
@@ -1367,19 +1367,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="30">
@@ -1387,7 +1387,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1600</v>
+        <v>1616</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="G2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="H2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="I2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -1630,16 +1630,16 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="M2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="N2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="O2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -1648,13 +1648,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3652</v>
+        <v>3656</v>
       </c>
       <c r="S2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="T2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2000</v>
+        <v>2012</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1721,10 +1721,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="K3" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="Q3" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1754,10 +1754,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="V3" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5709</v>
+        <v>5712</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1912,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>19981.5</v>
+        <v>19992</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>19981.5</v>
+        <v>19971</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -2121,7 +2121,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2854.5</v>
+        <v>2856</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2854.5</v>
+        <v>2853</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -2224,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>951.5</v>
+        <v>952</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>951.5</v>
+        <v>951</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -2571,13 +2571,13 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="K2" t="n">
-        <v>7612</v>
+        <v>7608</v>
       </c>
       <c r="L2" t="n">
-        <v>11418</v>
+        <v>11412</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2589,13 +2589,13 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="Q2" t="n">
-        <v>7612</v>
+        <v>7608</v>
       </c>
       <c r="R2" t="n">
-        <v>11418</v>
+        <v>11412</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>3652</v>
+        <v>3656</v>
       </c>
       <c r="W2" t="n">
-        <v>7458</v>
+        <v>7460</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>5709</v>
+        <v>5706</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -2956,25 +2956,25 @@
         <v>3200</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3174,22 +3174,22 @@
         <v>398</v>
       </c>
       <c r="Q8" t="n">
-        <v>1181.5</v>
+        <v>1182</v>
       </c>
       <c r="R8" t="n">
-        <v>1000.5</v>
+        <v>1001</v>
       </c>
       <c r="S8" t="n">
-        <v>812.5</v>
+        <v>813</v>
       </c>
       <c r="T8" t="n">
-        <v>600.5</v>
+        <v>601</v>
       </c>
       <c r="U8" t="n">
-        <v>347.5</v>
+        <v>348</v>
       </c>
       <c r="V8" t="n">
-        <v>128.5</v>
+        <v>129</v>
       </c>
       <c r="W8" t="n">
         <v>884</v>

--- a/output_5a.xlsx
+++ b/output_5a.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,6 +521,26 @@
       </c>
       <c r="B10" t="n">
         <v>14.12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>New capacity WS-X (units)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>New capacity WS-Y (min)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11412</v>
       </c>
     </row>
   </sheetData>
@@ -534,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,6 +603,11 @@
           <t>Modernization Cost Y (EUR)</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Grand Total (EUR)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -606,6 +631,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -629,6 +655,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -652,6 +679,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -675,6 +703,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -698,6 +727,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -721,6 +751,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -744,6 +775,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -774,6 +806,9 @@
       </c>
       <c r="I9" t="n">
         <v>21180</v>
+      </c>
+      <c r="J9" t="n">
+        <v>510076.6</v>
       </c>
     </row>
   </sheetData>

--- a/output_5a.xlsx
+++ b/output_5a.xlsx
@@ -1102,7 +1102,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>-0</v>
@@ -1111,7 +1111,7 @@
         <v>-0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>-0</v>
@@ -1122,7 +1122,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
@@ -1131,7 +1131,7 @@
         <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
@@ -1165,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
